--- a/salidas/empresas/WELL.xlsx
+++ b/salidas/empresas/WELL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>14.42448806762695</v>
+        <v>14.4244909286499</v>
       </c>
       <c r="C2" t="n">
         <v>37.18999862670898</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>14.13747692108154</v>
+        <v>14.13748359680176</v>
       </c>
       <c r="C3" t="n">
         <v>36.45000076293945</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>14.77744197845459</v>
+        <v>14.77745151519775</v>
       </c>
       <c r="C4" t="n">
         <v>38.09999847412109</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>13.7485523223877</v>
+        <v>13.74855518341064</v>
       </c>
       <c r="C5" t="n">
         <v>34.79999923706055</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>13.38903522491455</v>
+        <v>13.38903903961182</v>
       </c>
       <c r="C6" t="n">
         <v>33.88999938964844</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>13.8078145980835</v>
+        <v>13.80781745910645</v>
       </c>
       <c r="C7" t="n">
         <v>34.95000076293945</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>14.5505542755127</v>
+        <v>14.55055332183838</v>
       </c>
       <c r="C8" t="n">
         <v>36.18999862670898</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>16.05827713012695</v>
+        <v>16.05827522277832</v>
       </c>
       <c r="C9" t="n">
         <v>39.93999862670898</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>16.08642578125</v>
+        <v>16.08642387390137</v>
       </c>
       <c r="C10" t="n">
         <v>40.0099983215332</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>16.85366630554199</v>
+        <v>16.85367393493652</v>
       </c>
       <c r="C11" t="n">
         <v>41.27999877929688</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>17.11905097961426</v>
+        <v>17.11905479431152</v>
       </c>
       <c r="C12" t="n">
         <v>41.93000030517578</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>17.71138000488281</v>
+        <v>17.71138191223145</v>
       </c>
       <c r="C13" t="n">
         <v>43.02000045776367</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>19.39655876159668</v>
+        <v>19.39656066894531</v>
       </c>
       <c r="C14" t="n">
         <v>46.81000137329102</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>18.56782913208008</v>
+        <v>18.56782150268555</v>
       </c>
       <c r="C15" t="n">
         <v>44.81000137329102</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>18.19074630737305</v>
+        <v>18.19075012207031</v>
       </c>
       <c r="C16" t="n">
         <v>43.90000152587891</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>18.74601364135742</v>
+        <v>18.74600219726562</v>
       </c>
       <c r="C17" t="n">
         <v>45.2400016784668</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>18.40855979919434</v>
+        <v>18.4085636138916</v>
       </c>
       <c r="C18" t="n">
         <v>43.77000045776367</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>16.97440338134766</v>
+        <v>16.97439575195312</v>
       </c>
       <c r="C19" t="n">
         <v>40.36000061035156</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>15.43930530548096</v>
+        <v>15.43930721282959</v>
       </c>
       <c r="C20" t="n">
         <v>36.70999908447266</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>17.08816528320312</v>
+        <v>17.08816146850586</v>
       </c>
       <c r="C21" t="n">
         <v>39.90000152587891</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>18.94687843322754</v>
+        <v>18.94687080383301</v>
       </c>
       <c r="C22" t="n">
         <v>44.2400016784668</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>19.2505054473877</v>
+        <v>19.25050735473633</v>
       </c>
       <c r="C23" t="n">
         <v>44.29000091552734</v>
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>19.47651863098145</v>
+        <v>19.47651672363281</v>
       </c>
       <c r="C24" t="n">
         <v>44.81000137329102</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>19.42436790466309</v>
+        <v>19.42435646057129</v>
       </c>
       <c r="C25" t="n">
         <v>44.68999862670898</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>18.8923397064209</v>
+        <v>18.89234733581543</v>
       </c>
       <c r="C26" t="n">
         <v>42.81999969482422</v>
@@ -957,7 +969,7 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>19.91152954101562</v>
+        <v>19.91152572631836</v>
       </c>
       <c r="C28" t="n">
         <v>45.13000106811523</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>21.67412567138672</v>
+        <v>21.67412185668945</v>
       </c>
       <c r="C29" t="n">
         <v>48.45000076293945</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>21.60702514648438</v>
+        <v>21.60701942443848</v>
       </c>
       <c r="C30" t="n">
         <v>48.29999923706055</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>19.90709495544434</v>
+        <v>19.90709114074707</v>
       </c>
       <c r="C31" t="n">
         <v>44.5</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>22.61977767944336</v>
+        <v>22.61977958679199</v>
       </c>
       <c r="C32" t="n">
         <v>49.86999893188477</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>23.52693176269531</v>
+        <v>23.52693939208984</v>
       </c>
       <c r="C33" t="n">
         <v>51.86999893188477</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>24.14380645751953</v>
+        <v>24.14379692077637</v>
       </c>
       <c r="C34" t="n">
         <v>53.22999954223633</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>20.18862342834473</v>
+        <v>20.18862724304199</v>
       </c>
       <c r="C35" t="n">
         <v>44.5099983215332</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>17.5289249420166</v>
+        <v>17.52893257141113</v>
       </c>
       <c r="C36" t="n">
         <v>38</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>19.46634101867676</v>
+        <v>19.46633720397949</v>
       </c>
       <c r="C37" t="n">
         <v>42.20000076293945</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>17.44128799438477</v>
+        <v>17.44129753112793</v>
       </c>
       <c r="C38" t="n">
         <v>37.81000137329102</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>14.46000480651855</v>
+        <v>14.46000385284424</v>
       </c>
       <c r="C39" t="n">
         <v>30.77000045776367</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>14.37541389465332</v>
+        <v>14.37542057037354</v>
       </c>
       <c r="C40" t="n">
         <v>30.59000015258789</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>16.01079940795898</v>
+        <v>16.01079750061035</v>
       </c>
       <c r="C41" t="n">
         <v>34.06999969482422</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>16.42239761352539</v>
+        <v>16.42239379882812</v>
       </c>
       <c r="C42" t="n">
         <v>34.25</v>
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>16.3504753112793</v>
+        <v>16.35047149658203</v>
       </c>
       <c r="C43" t="n">
         <v>34.09999847412109</v>
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>19.20820999145508</v>
+        <v>19.20821189880371</v>
       </c>
       <c r="C44" t="n">
         <v>40.06000137329102</v>
@@ -1299,11 +1311,11 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>20.8012752532959</v>
+        <v>20.80127716064453</v>
       </c>
       <c r="C45" t="n">
         <v>42.70999908447266</v>
@@ -1318,11 +1330,11 @@
       <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>20.27041435241699</v>
+        <v>20.27039909362793</v>
       </c>
       <c r="C46" t="n">
         <v>41.61999893188477</v>
@@ -1337,11 +1349,11 @@
       <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>21.60976219177246</v>
+        <v>21.60975074768066</v>
       </c>
       <c r="C47" t="n">
         <v>44.36999893188477</v>
@@ -1356,11 +1368,11 @@
       <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>22.04014015197754</v>
+        <v>22.04013824462891</v>
       </c>
       <c r="C48" t="n">
         <v>44.54999923706055</v>
@@ -1375,11 +1387,11 @@
       <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>21.92636299133301</v>
+        <v>21.92636108398438</v>
       </c>
       <c r="C49" t="n">
         <v>44.31999969482422</v>
@@ -1394,11 +1406,11 @@
       <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>21.27331161499023</v>
+        <v>21.27331352233887</v>
       </c>
       <c r="C50" t="n">
         <v>43</v>
@@ -1413,11 +1425,11 @@
       <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>21.29551124572754</v>
+        <v>21.29549217224121</v>
       </c>
       <c r="C51" t="n">
         <v>42.36000061035156</v>
@@ -1432,11 +1444,11 @@
       <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>22.73833465576172</v>
+        <v>22.73831939697266</v>
       </c>
       <c r="C52" t="n">
         <v>45.22999954223633</v>
@@ -1451,11 +1463,11 @@
       <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>22.58750915527344</v>
+        <v>22.58750534057617</v>
       </c>
       <c r="C53" t="n">
         <v>44.93000030517578</v>
@@ -1470,11 +1482,11 @@
       <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>22.00115013122559</v>
+        <v>22.00115966796875</v>
       </c>
       <c r="C54" t="n">
         <v>43.08000183105469</v>
@@ -1489,11 +1501,11 @@
       <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>21.51087379455566</v>
+        <v>21.51087760925293</v>
       </c>
       <c r="C55" t="n">
         <v>42.11999893188477</v>
@@ -1508,11 +1520,11 @@
       <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>23.14002418518066</v>
+        <v>23.14002799987793</v>
       </c>
       <c r="C56" t="n">
         <v>45.31000137329102</v>
@@ -1527,11 +1539,11 @@
       <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>23.81379318237305</v>
+        <v>23.81379890441895</v>
       </c>
       <c r="C57" t="n">
         <v>45.93000030517578</v>
@@ -1552,11 +1564,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>24.54484939575195</v>
+        <v>24.54485321044922</v>
       </c>
       <c r="C58" t="n">
         <v>47.34000015258789</v>
@@ -1577,7 +1589,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
@@ -1602,11 +1614,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>24.32845115661621</v>
+        <v>24.32845306396484</v>
       </c>
       <c r="C60" t="n">
         <v>46.27999877929688</v>
@@ -1627,11 +1639,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>25.04338455200195</v>
+        <v>25.04338645935059</v>
       </c>
       <c r="C61" t="n">
         <v>47.63999938964844</v>
@@ -1652,11 +1664,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>25.80036163330078</v>
+        <v>25.80035781860352</v>
       </c>
       <c r="C62" t="n">
         <v>49.08000183105469</v>
@@ -1677,11 +1689,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>27.84033584594727</v>
+        <v>27.84033393859863</v>
       </c>
       <c r="C63" t="n">
         <v>52.22000122070312</v>
@@ -1702,11 +1714,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>27.95762252807617</v>
+        <v>27.95761680603027</v>
       </c>
       <c r="C64" t="n">
         <v>52.43999862670898</v>
@@ -1731,11 +1743,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>28.66669273376465</v>
+        <v>28.66670227050781</v>
       </c>
       <c r="C65" t="n">
         <v>53.77000045776367</v>
@@ -1760,11 +1772,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>28.74826431274414</v>
+        <v>28.74825286865234</v>
       </c>
       <c r="C66" t="n">
         <v>53.18999862670898</v>
@@ -1789,11 +1801,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>28.33749389648438</v>
+        <v>28.33748817443848</v>
       </c>
       <c r="C67" t="n">
         <v>52.43000030517578</v>
@@ -1818,11 +1830,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>28.52665710449219</v>
+        <v>28.52665138244629</v>
       </c>
       <c r="C68" t="n">
         <v>52.77999877929688</v>
@@ -1847,11 +1859,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>27.96571731567383</v>
+        <v>27.9657154083252</v>
       </c>
       <c r="C69" t="n">
         <v>50.95999908447266</v>
@@ -1876,11 +1888,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>25.68279647827148</v>
+        <v>25.68280410766602</v>
       </c>
       <c r="C70" t="n">
         <v>46.79999923706055</v>
@@ -1905,11 +1917,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>28.91510009765625</v>
+        <v>28.91510963439941</v>
       </c>
       <c r="C71" t="n">
         <v>52.68999862670898</v>
@@ -1934,11 +1946,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>27.90875244140625</v>
+        <v>27.90876197814941</v>
       </c>
       <c r="C72" t="n">
         <v>50.16999816894531</v>
@@ -1963,11 +1975,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>30.33416557312012</v>
+        <v>30.33415985107422</v>
       </c>
       <c r="C73" t="n">
         <v>54.52999877929688</v>
@@ -1992,11 +2004,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>31.82499504089355</v>
+        <v>31.82499694824219</v>
       </c>
       <c r="C74" t="n">
         <v>57.20999908447266</v>
@@ -2021,7 +2033,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
@@ -2050,7 +2062,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
@@ -2079,11 +2091,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>31.95448112487793</v>
+        <v>31.9544677734375</v>
       </c>
       <c r="C77" t="n">
         <v>56.70000076293945</v>
@@ -2108,7 +2120,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
@@ -2137,11 +2149,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>33.28849792480469</v>
+        <v>33.28850936889648</v>
       </c>
       <c r="C79" t="n">
         <v>58.29999923706055</v>
@@ -2166,11 +2178,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>35.53247451782227</v>
+        <v>35.5324821472168</v>
       </c>
       <c r="C80" t="n">
         <v>62.22999954223633</v>
@@ -2195,7 +2207,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
@@ -2224,7 +2236,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
@@ -2253,11 +2265,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>34.34237289428711</v>
+        <v>34.34236526489258</v>
       </c>
       <c r="C83" t="n">
         <v>59.43000030517578</v>
@@ -2282,11 +2294,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>34.45983123779297</v>
+        <v>34.45981979370117</v>
       </c>
       <c r="C84" t="n">
         <v>58.88999938964844</v>
@@ -2311,7 +2323,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
@@ -2340,11 +2352,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>36.77119064331055</v>
+        <v>36.77118682861328</v>
       </c>
       <c r="C86" t="n">
         <v>62.84000015258789</v>
@@ -2369,11 +2381,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>37.99443054199219</v>
+        <v>37.99441909790039</v>
       </c>
       <c r="C87" t="n">
         <v>64.13999938964844</v>
@@ -2398,11 +2410,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>40.22764587402344</v>
+        <v>40.22765350341797</v>
       </c>
       <c r="C88" t="n">
         <v>67.91000366210938</v>
@@ -2427,11 +2439,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>44.40975189208984</v>
+        <v>44.40977478027344</v>
       </c>
       <c r="C89" t="n">
         <v>74.97000122070312</v>
@@ -2456,11 +2468,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>40.71080780029297</v>
+        <v>40.7108039855957</v>
       </c>
       <c r="C90" t="n">
         <v>68.02999877929688</v>
@@ -2485,7 +2497,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
@@ -2514,11 +2526,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>38.59237289428711</v>
+        <v>38.59238433837891</v>
       </c>
       <c r="C92" t="n">
         <v>64.48999786376953</v>
@@ -2543,11 +2555,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>37.21496200561523</v>
+        <v>37.21495819091797</v>
       </c>
       <c r="C93" t="n">
         <v>61.43999862670898</v>
@@ -2572,7 +2584,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
@@ -2601,11 +2613,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>39.28044128417969</v>
+        <v>39.28044509887695</v>
       </c>
       <c r="C95" t="n">
         <v>64.84999847412109</v>
@@ -2630,11 +2642,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>34.32889175415039</v>
+        <v>34.32890319824219</v>
       </c>
       <c r="C96" t="n">
         <v>55.9900016784668</v>
@@ -2659,11 +2671,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>32.84514236450195</v>
+        <v>32.84512710571289</v>
       </c>
       <c r="C97" t="n">
         <v>53.56999969482422</v>
@@ -2688,11 +2700,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>35.51223754882812</v>
+        <v>35.51223373413086</v>
       </c>
       <c r="C98" t="n">
         <v>57.91999816894531</v>
@@ -2717,11 +2729,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>36.52522277832031</v>
+        <v>36.52522659301758</v>
       </c>
       <c r="C99" t="n">
         <v>58.7400016784668</v>
@@ -2746,7 +2758,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
@@ -2775,7 +2787,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
@@ -2804,11 +2816,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>39.81462478637695</v>
+        <v>39.81460952758789</v>
       </c>
       <c r="C102" t="n">
         <v>63.22999954223633</v>
@@ -2833,11 +2845,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>39.46200180053711</v>
+        <v>39.46199417114258</v>
       </c>
       <c r="C103" t="n">
         <v>62.66999816894531</v>
@@ -2862,11 +2874,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>40.06649780273438</v>
+        <v>40.06647491455078</v>
       </c>
       <c r="C104" t="n">
         <v>63.63000106811523</v>
@@ -2891,11 +2903,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>43.0881233215332</v>
+        <v>43.08811569213867</v>
       </c>
       <c r="C105" t="n">
         <v>67.58000183105469</v>
@@ -2920,11 +2932,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>39.76630401611328</v>
+        <v>39.76629257202148</v>
       </c>
       <c r="C106" t="n">
         <v>62.36999893188477</v>
@@ -2949,11 +2961,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>45.33879470825195</v>
+        <v>45.33880233764648</v>
       </c>
       <c r="C107" t="n">
         <v>71.11000061035156</v>
@@ -2978,11 +2990,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>47.4921989440918</v>
+        <v>47.49220275878906</v>
       </c>
       <c r="C108" t="n">
         <v>73.66000366210938</v>
@@ -3007,11 +3019,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>48.78815078735352</v>
+        <v>48.78814697265625</v>
       </c>
       <c r="C109" t="n">
         <v>75.66999816894531</v>
@@ -3036,11 +3048,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>52.83713912963867</v>
+        <v>52.83715438842773</v>
       </c>
       <c r="C110" t="n">
         <v>81.94999694824219</v>
@@ -3065,11 +3077,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>50.22417449951172</v>
+        <v>50.22417068481445</v>
       </c>
       <c r="C111" t="n">
         <v>77.11000061035156</v>
@@ -3094,7 +3106,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
@@ -3123,11 +3135,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>46.90888977050781</v>
+        <v>46.90888595581055</v>
       </c>
       <c r="C113" t="n">
         <v>72.01999664306641</v>
@@ -3152,7 +3164,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
@@ -3181,7 +3193,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
@@ -3210,11 +3222,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>45.71052169799805</v>
+        <v>45.71051406860352</v>
       </c>
       <c r="C116" t="n">
         <v>69.37000274658203</v>
@@ -3239,11 +3251,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>42.2526741027832</v>
+        <v>42.25266265869141</v>
       </c>
       <c r="C117" t="n">
         <v>63.34999847412109</v>
@@ -3268,11 +3280,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>45.16733169555664</v>
+        <v>45.16732406616211</v>
       </c>
       <c r="C118" t="n">
         <v>67.72000122070312</v>
@@ -3297,11 +3309,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>43.2664680480957</v>
+        <v>43.26646041870117</v>
       </c>
       <c r="C119" t="n">
         <v>64.87000274658203</v>
@@ -3326,7 +3338,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
@@ -3355,11 +3367,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>45.95813369750977</v>
+        <v>45.95812606811523</v>
       </c>
       <c r="C121" t="n">
         <v>68.02999877929688</v>
@@ -3384,11 +3396,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>42.03313827514648</v>
+        <v>42.03314971923828</v>
       </c>
       <c r="C122" t="n">
         <v>62.22000122070312</v>
@@ -3413,11 +3425,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>43.67678451538086</v>
+        <v>43.6767692565918</v>
       </c>
       <c r="C123" t="n">
         <v>63.77999877929688</v>
@@ -3442,11 +3454,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>47.48428344726562</v>
+        <v>47.48427200317383</v>
       </c>
       <c r="C124" t="n">
         <v>69.33999633789062</v>
@@ -3471,11 +3483,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>47.53905487060547</v>
+        <v>47.53907012939453</v>
       </c>
       <c r="C125" t="n">
         <v>69.41999816894531</v>
@@ -3500,7 +3512,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
@@ -3529,11 +3541,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>52.77708435058594</v>
+        <v>52.777099609375</v>
       </c>
       <c r="C127" t="n">
         <v>76.16999816894531</v>
@@ -3558,11 +3570,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>54.96662139892578</v>
+        <v>54.96660995483398</v>
       </c>
       <c r="C128" t="n">
         <v>79.33000183105469</v>
@@ -3587,11 +3599,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>53.77405166625977</v>
+        <v>53.77407455444336</v>
       </c>
       <c r="C129" t="n">
         <v>76.75</v>
@@ -3616,7 +3628,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
@@ -3645,7 +3657,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
@@ -3674,11 +3686,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>44.5670280456543</v>
+        <v>44.56703186035156</v>
       </c>
       <c r="C132" t="n">
         <v>62.77999877929688</v>
@@ -3703,11 +3715,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>47.51308059692383</v>
+        <v>47.51308441162109</v>
       </c>
       <c r="C133" t="n">
         <v>66.93000030517578</v>
@@ -3732,11 +3744,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>47.06586456298828</v>
+        <v>47.06585311889648</v>
       </c>
       <c r="C134" t="n">
         <v>66.30000305175781</v>
@@ -3761,11 +3773,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>50.62613296508789</v>
+        <v>50.62614059448242</v>
       </c>
       <c r="C135" t="n">
         <v>70.37999725341797</v>
@@ -3790,11 +3802,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>50.94264221191406</v>
+        <v>50.94264602661133</v>
       </c>
       <c r="C136" t="n">
         <v>70.81999969482422</v>
@@ -3819,11 +3831,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>51.38862228393555</v>
+        <v>51.38862991333008</v>
       </c>
       <c r="C137" t="n">
         <v>71.44000244140625</v>
@@ -3848,11 +3860,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>52.83788299560547</v>
+        <v>52.83790969848633</v>
       </c>
       <c r="C138" t="n">
         <v>72.54000091552734</v>
@@ -3877,11 +3889,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>54.52050018310547</v>
+        <v>54.52048873901367</v>
       </c>
       <c r="C139" t="n">
         <v>74.84999847412109</v>
@@ -3906,11 +3918,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>53.45703125</v>
+        <v>53.45703887939453</v>
       </c>
       <c r="C140" t="n">
         <v>73.38999938964844</v>
@@ -3935,11 +3947,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>53.9759407043457</v>
+        <v>53.9759635925293</v>
       </c>
       <c r="C141" t="n">
         <v>73.22000122070312</v>
@@ -3964,11 +3976,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>51.80866622924805</v>
+        <v>51.80867004394531</v>
       </c>
       <c r="C142" t="n">
         <v>70.27999877929688</v>
@@ -3993,11 +4005,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>49.36122894287109</v>
+        <v>49.36125183105469</v>
       </c>
       <c r="C143" t="n">
         <v>66.95999908447266</v>
@@ -4022,7 +4034,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
@@ -4051,7 +4063,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
@@ -4080,11 +4092,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>44.78004837036133</v>
+        <v>44.78004455566406</v>
       </c>
       <c r="C146" t="n">
         <v>59.97000122070312</v>
@@ -4109,11 +4121,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>39.82668304443359</v>
+        <v>39.82667922973633</v>
       </c>
       <c r="C147" t="n">
         <v>52.5</v>
@@ -4138,11 +4150,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>41.29077911376953</v>
+        <v>41.29078674316406</v>
       </c>
       <c r="C148" t="n">
         <v>54.43000030517578</v>
@@ -4167,11 +4179,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>40.53976058959961</v>
+        <v>40.53976440429688</v>
       </c>
       <c r="C149" t="n">
         <v>53.43999862670898</v>
@@ -4196,11 +4208,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>44.42139434814453</v>
+        <v>44.42138671875</v>
       </c>
       <c r="C150" t="n">
         <v>57.65000152587891</v>
@@ -4225,11 +4237,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>48.30488967895508</v>
+        <v>48.30489349365234</v>
       </c>
       <c r="C151" t="n">
         <v>62.68999862670898</v>
@@ -4254,11 +4266,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>48.23553848266602</v>
+        <v>48.23555374145508</v>
       </c>
       <c r="C152" t="n">
         <v>62.59999847412109</v>
@@ -4283,11 +4295,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>52.10725021362305</v>
+        <v>52.10724639892578</v>
       </c>
       <c r="C153" t="n">
         <v>66.70999908447266</v>
@@ -4312,11 +4324,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>50.24042892456055</v>
+        <v>50.24042129516602</v>
       </c>
       <c r="C154" t="n">
         <v>64.31999969482422</v>
@@ -4341,11 +4353,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>51.60734939575195</v>
+        <v>51.60734558105469</v>
       </c>
       <c r="C155" t="n">
         <v>66.06999969482422</v>
@@ -4370,11 +4382,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>57.21745300292969</v>
+        <v>57.21743774414062</v>
       </c>
       <c r="C156" t="n">
         <v>72.33000183105469</v>
@@ -4399,11 +4411,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>54.90755462646484</v>
+        <v>54.90754699707031</v>
       </c>
       <c r="C157" t="n">
         <v>69.41000366210938</v>
@@ -4428,11 +4440,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>61.29932403564453</v>
+        <v>61.29931640625</v>
       </c>
       <c r="C158" t="n">
         <v>77.48999786376953</v>
@@ -4457,11 +4469,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>59.46674346923828</v>
+        <v>59.46673202514648</v>
       </c>
       <c r="C159" t="n">
         <v>74.30999755859375</v>
@@ -4486,11 +4498,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>62.09956741333008</v>
+        <v>62.09954071044922</v>
       </c>
       <c r="C160" t="n">
         <v>77.59999847412109</v>
@@ -4515,11 +4527,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>59.64278411865234</v>
+        <v>59.64276885986328</v>
       </c>
       <c r="C161" t="n">
         <v>74.52999877929688</v>
@@ -4544,11 +4556,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>65.73410034179688</v>
+        <v>65.73409271240234</v>
       </c>
       <c r="C162" t="n">
         <v>81.22000122070312</v>
@@ -4573,7 +4585,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
@@ -4602,11 +4614,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>67.27182769775391</v>
+        <v>67.27184295654297</v>
       </c>
       <c r="C164" t="n">
         <v>83.12000274658203</v>
@@ -4631,11 +4643,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>73.20896148681641</v>
+        <v>73.20894622802734</v>
       </c>
       <c r="C165" t="n">
         <v>89.55999755859375</v>
@@ -4660,11 +4672,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>74.09996032714844</v>
+        <v>74.09995269775391</v>
       </c>
       <c r="C166" t="n">
         <v>90.65000152587891</v>
@@ -4689,11 +4701,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>74.13262939453125</v>
+        <v>74.13263702392578</v>
       </c>
       <c r="C167" t="n">
         <v>90.69000244140625</v>
@@ -4718,11 +4730,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>69.86128997802734</v>
+        <v>69.86128234863281</v>
       </c>
       <c r="C168" t="n">
         <v>84.56999969482422</v>
@@ -4747,11 +4759,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>67.55653381347656</v>
+        <v>67.55651092529297</v>
       </c>
       <c r="C169" t="n">
         <v>81.77999877929688</v>
@@ -4776,7 +4788,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
@@ -4805,7 +4817,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
@@ -4834,11 +4846,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>38.1953125</v>
+        <v>38.19530868530273</v>
       </c>
       <c r="C172" t="n">
         <v>45.77999877929688</v>
@@ -4863,11 +4875,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>42.74236679077148</v>
+        <v>42.74237060546875</v>
       </c>
       <c r="C173" t="n">
         <v>51.22999954223633</v>
@@ -4892,11 +4904,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>42.9192008972168</v>
+        <v>42.91919326782227</v>
       </c>
       <c r="C174" t="n">
         <v>50.66999816894531</v>
@@ -4921,7 +4933,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
@@ -4950,11 +4962,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>45.36712265014648</v>
+        <v>45.36713027954102</v>
       </c>
       <c r="C176" t="n">
         <v>53.56000137329102</v>
@@ -4979,11 +4991,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>49.25077438354492</v>
+        <v>49.25077819824219</v>
       </c>
       <c r="C177" t="n">
         <v>57.52000045776367</v>
@@ -5008,11 +5020,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>47.17012023925781</v>
+        <v>47.17011642456055</v>
       </c>
       <c r="C178" t="n">
         <v>55.09000015258789</v>
@@ -5037,11 +5049,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>46.03988647460938</v>
+        <v>46.03989028930664</v>
       </c>
       <c r="C179" t="n">
         <v>53.77000045776367</v>
@@ -5066,11 +5078,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>54.52512741088867</v>
+        <v>54.52511978149414</v>
       </c>
       <c r="C180" t="n">
         <v>62.97999954223633</v>
@@ -5095,11 +5107,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>55.9449462890625</v>
+        <v>55.94496154785156</v>
       </c>
       <c r="C181" t="n">
         <v>64.62000274658203</v>
@@ -5124,11 +5136,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>52.46461868286133</v>
+        <v>52.46462249755859</v>
       </c>
       <c r="C182" t="n">
         <v>60.59999847412109</v>
@@ -5153,11 +5165,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>59.31538772583008</v>
+        <v>59.31538009643555</v>
       </c>
       <c r="C183" t="n">
         <v>67.90000152587891</v>
@@ -5182,11 +5194,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>62.57380294799805</v>
+        <v>62.57378768920898</v>
       </c>
       <c r="C184" t="n">
         <v>71.62999725341797</v>
@@ -5211,11 +5223,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>65.5439453125</v>
+        <v>65.54393005371094</v>
       </c>
       <c r="C185" t="n">
         <v>75.02999877929688</v>
@@ -5240,11 +5252,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>65.85458374023438</v>
+        <v>65.85457611083984</v>
       </c>
       <c r="C186" t="n">
         <v>74.76999664306641</v>
@@ -5269,7 +5281,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
@@ -5298,11 +5310,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>76.50299072265625</v>
+        <v>76.50300598144531</v>
       </c>
       <c r="C188" t="n">
         <v>86.86000061035156</v>
@@ -5327,7 +5339,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
@@ -5356,11 +5368,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>73.09913635253906</v>
+        <v>73.09914398193359</v>
       </c>
       <c r="C190" t="n">
         <v>82.40000152587891</v>
@@ -5385,7 +5397,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
@@ -5414,7 +5426,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
@@ -5443,11 +5455,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>76.63519287109375</v>
+        <v>76.63520050048828</v>
       </c>
       <c r="C193" t="n">
         <v>85.76999664306641</v>
@@ -5472,7 +5484,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
@@ -5501,11 +5513,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>74.96169281005859</v>
+        <v>74.96168518066406</v>
       </c>
       <c r="C195" t="n">
         <v>83.29000091552734</v>
@@ -5530,11 +5542,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>86.52678680419922</v>
+        <v>86.52679443359375</v>
       </c>
       <c r="C196" t="n">
         <v>96.13999938964844</v>
@@ -5559,11 +5571,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>81.72974395751953</v>
+        <v>81.72975921630859</v>
       </c>
       <c r="C197" t="n">
         <v>90.80999755859375</v>
@@ -5588,11 +5600,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>80.74069213867188</v>
+        <v>80.74071502685547</v>
       </c>
       <c r="C198" t="n">
         <v>89.08999633789062</v>
@@ -5617,11 +5629,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>74.63236999511719</v>
+        <v>74.63235473632812</v>
       </c>
       <c r="C199" t="n">
         <v>82.34999847412109</v>
@@ -5646,11 +5658,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>78.24844360351562</v>
+        <v>78.24843597412109</v>
       </c>
       <c r="C200" t="n">
         <v>86.33999633789062</v>
@@ -5675,11 +5687,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>70.00315856933594</v>
+        <v>70.00314331054688</v>
       </c>
       <c r="C201" t="n">
         <v>76.65000152587891</v>
@@ -5704,11 +5716,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>58.74236297607422</v>
+        <v>58.74237060546875</v>
       </c>
       <c r="C202" t="n">
         <v>64.31999969482422</v>
@@ -5733,11 +5745,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>55.74680328369141</v>
+        <v>55.74679183959961</v>
       </c>
       <c r="C203" t="n">
         <v>61.04000091552734</v>
@@ -5762,11 +5774,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>65.45595550537109</v>
+        <v>65.45594787597656</v>
       </c>
       <c r="C204" t="n">
         <v>71.02999877929688</v>
@@ -5791,7 +5803,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
@@ -5820,11 +5832,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>69.15128326416016</v>
+        <v>69.15127563476562</v>
       </c>
       <c r="C206" t="n">
         <v>75.04000091552734</v>
@@ -5849,11 +5861,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>68.86453247070312</v>
+        <v>68.86454772949219</v>
       </c>
       <c r="C207" t="n">
         <v>74.12000274658203</v>
@@ -5878,7 +5890,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
@@ -5907,7 +5919,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
@@ -5936,7 +5948,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
@@ -5965,11 +5977,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>75.73710632324219</v>
+        <v>75.73709869384766</v>
       </c>
       <c r="C211" t="n">
         <v>80.88999938964844</v>
@@ -5994,11 +6006,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>76.91683959960938</v>
+        <v>76.91684722900391</v>
       </c>
       <c r="C212" t="n">
         <v>82.15000152587891</v>
@@ -6023,11 +6035,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>78.16622924804688</v>
+        <v>78.16623687744141</v>
       </c>
       <c r="C213" t="n">
         <v>82.87999725341797</v>
@@ -6052,7 +6064,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
@@ -6081,11 +6093,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>78.85470581054688</v>
+        <v>78.85469818115234</v>
       </c>
       <c r="C215" t="n">
         <v>83.61000061035156</v>
@@ -6110,11 +6122,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>84.63291168212891</v>
+        <v>84.63291931152344</v>
       </c>
       <c r="C216" t="n">
         <v>89.09999847412109</v>
@@ -6139,7 +6151,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
@@ -6168,11 +6180,11 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>82.17275238037109</v>
+        <v>82.17276763916016</v>
       </c>
       <c r="C218" t="n">
         <v>86.51000213623047</v>
@@ -6197,11 +6209,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>88.10974884033203</v>
+        <v>88.10975646972656</v>
       </c>
       <c r="C219" t="n">
         <v>92.16000366210938</v>
@@ -6226,7 +6238,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
@@ -6255,11 +6267,11 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>91.09264373779297</v>
+        <v>91.09263610839844</v>
       </c>
       <c r="C221" t="n">
         <v>95.27999877929688</v>
@@ -6284,11 +6296,11 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>99.72740173339844</v>
+        <v>99.72740936279297</v>
       </c>
       <c r="C222" t="n">
         <v>103.6699981689453</v>
@@ -6313,11 +6325,11 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>100.2853393554688</v>
+        <v>100.2853546142578</v>
       </c>
       <c r="C223" t="n">
         <v>104.25</v>
@@ -6342,11 +6354,11 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>107.0191268920898</v>
+        <v>107.0191421508789</v>
       </c>
       <c r="C224" t="n">
         <v>111.25</v>
@@ -6371,11 +6383,11 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>116.7568435668945</v>
+        <v>116.7568359375</v>
       </c>
       <c r="C225" t="n">
         <v>120.6800003051758</v>
@@ -6400,11 +6412,11 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>123.8679046630859</v>
+        <v>123.8678970336914</v>
       </c>
       <c r="C226" t="n">
         <v>128.0299987792969</v>
@@ -6429,11 +6441,11 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>130.4952087402344</v>
+        <v>130.4952392578125</v>
       </c>
       <c r="C227" t="n">
         <v>134.8800048828125</v>
@@ -6458,11 +6470,11 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>134.3499908447266</v>
+        <v>134.3500061035156</v>
       </c>
       <c r="C228" t="n">
         <v>138.1799926757812</v>
@@ -6487,11 +6499,11 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>122.5367660522461</v>
+        <v>122.536750793457</v>
       </c>
       <c r="C229" t="n">
         <v>126.0299987792969</v>
@@ -6516,7 +6528,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
@@ -6545,11 +6557,11 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>149.9218902587891</v>
+        <v>149.921875</v>
       </c>
       <c r="C231" t="n">
         <v>153.5099945068359</v>
@@ -6574,11 +6586,11 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>149.62890625</v>
+        <v>149.6289215087891</v>
       </c>
       <c r="C232" t="n">
         <v>153.2100067138672</v>
@@ -6603,7 +6615,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
@@ -6632,11 +6644,11 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>151.3719787597656</v>
+        <v>151.3719940185547</v>
       </c>
       <c r="C234" t="n">
         <v>154.2799987792969</v>
@@ -6661,7 +6673,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
@@ -6690,11 +6702,11 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>161.9586181640625</v>
+        <v>161.9586334228516</v>
       </c>
       <c r="C236" t="n">
         <v>165.0700073242188</v>
@@ -6719,7 +6731,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
@@ -6748,7 +6760,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -6777,11 +6789,11 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>178.4133148193359</v>
+        <v>178.413330078125</v>
       </c>
       <c r="C239" t="n">
         <v>181.0399932861328</v>
@@ -6806,11 +6818,11 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>206.000244140625</v>
+        <v>206.0002288818359</v>
       </c>
       <c r="C240" t="n">
         <v>208.2200012207031</v>
@@ -6835,7 +6847,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -6864,11 +6876,11 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
-        <v>186.3519744873047</v>
+        <v>186.3519592285156</v>
       </c>
       <c r="C242" t="n">
         <v>188.3600006103516</v>
@@ -6893,7 +6905,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -6922,7 +6934,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -6951,7 +6963,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -6980,7 +6992,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -7009,7 +7021,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7038,7 +7050,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7067,7 +7079,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7096,32 +7108,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>229.8699951171875</v>
+        <v>233.6100006103516</v>
       </c>
       <c r="C250" t="n">
-        <v>229.8699951171875</v>
+        <v>233.6100006103516</v>
       </c>
       <c r="D250" t="n">
-        <v>43399100</v>
+        <v>46150300</v>
       </c>
       <c r="E250" t="n">
         <v>2.17</v>
       </c>
       <c r="F250" t="n">
-        <v>105.9308733258929</v>
+        <v>107.6543781614523</v>
       </c>
       <c r="G250" t="n">
         <v>705914450</v>
       </c>
       <c r="H250" t="n">
-        <v>162268551174.6521</v>
+        <v>164908675095.356</v>
       </c>
       <c r="I250" t="n">
-        <v>0.06147926282002019</v>
+        <v>0.06537661893732308</v>
       </c>
     </row>
   </sheetData>
@@ -7153,75 +7165,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40626</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7257,13 +7269,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40396</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7299,13 +7311,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40490</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7341,13 +7353,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40087</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40178</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40626</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7374,7 +7386,7 @@
       <c r="I5" t="n">
         <v>1.52</v>
       </c>
-      <c r="J5" s="1" t="n">
+      <c r="J5" s="2" t="n">
         <v>40626</v>
       </c>
       <c r="K5" t="n">
@@ -7387,13 +7399,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40626</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7420,7 +7432,7 @@
       <c r="I6" t="n">
         <v>1.17</v>
       </c>
-      <c r="J6" s="1" t="n">
+      <c r="J6" s="2" t="n">
         <v>40626</v>
       </c>
       <c r="K6" t="n">
@@ -7433,13 +7445,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40396</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7466,7 +7478,7 @@
       <c r="I7" t="n">
         <v>1.01</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40626</v>
       </c>
       <c r="K7" t="n">
@@ -7479,13 +7491,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40490</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7512,7 +7524,7 @@
       <c r="I8" t="n">
         <v>0.85</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40626</v>
       </c>
       <c r="K8" t="n">
@@ -7525,13 +7537,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40626</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7558,7 +7570,7 @@
       <c r="I9" t="n">
         <v>0.8799999999999999</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40626</v>
       </c>
       <c r="K9" t="n">
@@ -7571,13 +7583,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40673</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7604,7 +7616,7 @@
       <c r="I10" t="n">
         <v>0.82</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40673</v>
       </c>
       <c r="K10" t="n">
@@ -7617,13 +7629,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40764</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7650,7 +7662,7 @@
       <c r="I11" t="n">
         <v>0.84</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40764</v>
       </c>
       <c r="K11" t="n">
@@ -7663,13 +7675,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40850</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7696,7 +7708,7 @@
       <c r="I12" t="n">
         <v>1.04</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40850</v>
       </c>
       <c r="K12" t="n">
@@ -7709,13 +7721,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40956</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7742,7 +7754,7 @@
       <c r="I13" t="n">
         <v>0.8999999999999999</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40956</v>
       </c>
       <c r="K13" t="n">
@@ -7755,13 +7767,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>41039</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7788,7 +7800,7 @@
       <c r="I14" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>41039</v>
       </c>
       <c r="K14" t="n">
@@ -7801,13 +7813,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>41127</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7834,7 +7846,7 @@
       <c r="I15" t="n">
         <v>0.8</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>41127</v>
       </c>
       <c r="K15" t="n">
@@ -7847,13 +7859,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41221</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7880,7 +7892,7 @@
       <c r="I16" t="n">
         <v>0.75</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41221</v>
       </c>
       <c r="K16" t="n">
@@ -7893,13 +7905,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41331</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7926,7 +7938,7 @@
       <c r="I17" t="n">
         <v>0.95</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41331</v>
       </c>
       <c r="K17" t="n">
@@ -7939,13 +7951,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41401</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -7972,7 +7984,7 @@
       <c r="I18" t="n">
         <v>0.97</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41401</v>
       </c>
       <c r="K18" t="n">
@@ -7985,13 +7997,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41492</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8018,7 +8030,7 @@
       <c r="I19" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41492</v>
       </c>
       <c r="K19" t="n">
@@ -8031,13 +8043,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41583</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8064,7 +8076,7 @@
       <c r="I20" t="n">
         <v>0.6</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41583</v>
       </c>
       <c r="K20" t="n">
@@ -8077,13 +8089,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41691</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8110,7 +8122,7 @@
       <c r="I21" t="n">
         <v>0.29</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41691</v>
       </c>
       <c r="K21" t="n">
@@ -8123,13 +8135,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41767</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8156,7 +8168,7 @@
       <c r="I22" t="n">
         <v>0.25</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41767</v>
       </c>
       <c r="K22" t="n">
@@ -8169,13 +8181,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41852</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8202,7 +8214,7 @@
       <c r="I23" t="n">
         <v>0.52</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41852</v>
       </c>
       <c r="K23" t="n">
@@ -8215,13 +8227,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41947</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8248,7 +8260,7 @@
       <c r="I24" t="n">
         <v>0.89</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41947</v>
       </c>
       <c r="K24" t="n">
@@ -8261,13 +8273,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>42055</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8294,7 +8306,7 @@
       <c r="I25" t="n">
         <v>1.42</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>42055</v>
       </c>
       <c r="K25" t="n">
@@ -8307,13 +8319,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>42132</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8340,7 +8352,7 @@
       <c r="I26" t="n">
         <v>1.81</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>42132</v>
       </c>
       <c r="K26" t="n">
@@ -8353,13 +8365,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42220</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8386,7 +8398,7 @@
       <c r="I27" t="n">
         <v>2.46</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42220</v>
       </c>
       <c r="K27" t="n">
@@ -8399,13 +8411,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42307</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8432,7 +8444,7 @@
       <c r="I28" t="n">
         <v>2.54</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42307</v>
       </c>
       <c r="K28" t="n">
@@ -8445,13 +8457,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42418</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8478,7 +8490,7 @@
       <c r="I29" t="n">
         <v>2.34</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42418</v>
       </c>
       <c r="K29" t="n">
@@ -8491,13 +8503,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42495</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8524,7 +8536,7 @@
       <c r="I30" t="n">
         <v>2.2</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42495</v>
       </c>
       <c r="K30" t="n">
@@ -8537,13 +8549,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42584</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8570,7 +8582,7 @@
       <c r="I31" t="n">
         <v>1.85</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42584</v>
       </c>
       <c r="K31" t="n">
@@ -8583,13 +8595,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42676</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8616,7 +8628,7 @@
       <c r="I32" t="n">
         <v>2.26</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42676</v>
       </c>
       <c r="K32" t="n">
@@ -8629,13 +8641,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42788</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8662,7 +8674,7 @@
       <c r="I33" t="n">
         <v>2.8</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42788</v>
       </c>
       <c r="K33" t="n">
@@ -8675,13 +8687,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42860</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8708,7 +8720,7 @@
       <c r="I34" t="n">
         <v>3.24</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42860</v>
       </c>
       <c r="K34" t="n">
@@ -8721,13 +8733,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42944</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8754,7 +8766,7 @@
       <c r="I35" t="n">
         <v>3.21</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42944</v>
       </c>
       <c r="K35" t="n">
@@ -8767,13 +8779,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>43046</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8800,7 +8812,7 @@
       <c r="I36" t="n">
         <v>2.48</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>43046</v>
       </c>
       <c r="K36" t="n">
@@ -8813,13 +8825,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8846,7 +8858,7 @@
       <c r="I37" t="n">
         <v>1.26</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="K37" t="n">
@@ -8859,13 +8871,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43224</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8892,7 +8904,7 @@
       <c r="I38" t="n">
         <v>1.57</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43224</v>
       </c>
       <c r="K38" t="n">
@@ -8905,13 +8917,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43314</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -8938,7 +8950,7 @@
       <c r="I39" t="n">
         <v>1.47</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43314</v>
       </c>
       <c r="K39" t="n">
@@ -8951,13 +8963,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43403</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -8984,7 +8996,7 @@
       <c r="I40" t="n">
         <v>1.44</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43403</v>
       </c>
       <c r="K40" t="n">
@@ -8997,13 +9009,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43521</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9030,7 +9042,7 @@
       <c r="I41" t="n">
         <v>2.02</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43521</v>
       </c>
       <c r="K41" t="n">
@@ -9043,13 +9055,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9076,7 +9088,7 @@
       <c r="I42" t="n">
         <v>1.56</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="K42" t="n">
@@ -9089,13 +9101,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43678</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9122,7 +9134,7 @@
       <c r="I43" t="n">
         <v>1.49</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43678</v>
       </c>
       <c r="K43" t="n">
@@ -9135,13 +9147,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43768</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9168,7 +9180,7 @@
       <c r="I44" t="n">
         <v>2.77</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43768</v>
       </c>
       <c r="K44" t="n">
@@ -9181,13 +9193,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43875</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9214,7 +9226,7 @@
       <c r="I45" t="n">
         <v>3.05</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43875</v>
       </c>
       <c r="K45" t="n">
@@ -9227,13 +9239,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43958</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9260,7 +9272,7 @@
       <c r="I46" t="n">
         <v>3.09</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43958</v>
       </c>
       <c r="K46" t="n">
@@ -9273,13 +9285,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>44049</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9306,7 +9318,7 @@
       <c r="I47" t="n">
         <v>3.17</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>44049</v>
       </c>
       <c r="K47" t="n">
@@ -9319,13 +9331,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>44133</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9352,7 +9364,7 @@
       <c r="I48" t="n">
         <v>2.49</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>44133</v>
       </c>
       <c r="K48" t="n">
@@ -9365,13 +9377,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44237</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9398,7 +9410,7 @@
       <c r="I49" t="n">
         <v>2.33</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44237</v>
       </c>
       <c r="K49" t="n">
@@ -9411,13 +9423,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44315</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9444,7 +9456,7 @@
       <c r="I50" t="n">
         <v>1.75</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44315</v>
       </c>
       <c r="K50" t="n">
@@ -9457,13 +9469,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44407</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9490,7 +9502,7 @@
       <c r="I51" t="n">
         <v>1.39</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44407</v>
       </c>
       <c r="K51" t="n">
@@ -9503,13 +9515,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44505</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9536,7 +9548,7 @@
       <c r="I52" t="n">
         <v>1.04</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44505</v>
       </c>
       <c r="K52" t="n">
@@ -9549,13 +9561,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44608</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9582,7 +9594,7 @@
       <c r="I53" t="n">
         <v>0.78</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44608</v>
       </c>
       <c r="K53" t="n">
@@ -9595,13 +9607,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44691</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9628,7 +9640,7 @@
       <c r="I54" t="n">
         <v>0.75</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44691</v>
       </c>
       <c r="K54" t="n">
@@ -9641,13 +9653,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44782</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9674,7 +9686,7 @@
       <c r="I55" t="n">
         <v>0.8900000000000001</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44782</v>
       </c>
       <c r="K55" t="n">
@@ -9687,13 +9699,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44873</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9720,7 +9732,7 @@
       <c r="I56" t="n">
         <v>0.46</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44873</v>
       </c>
       <c r="K56" t="n">
@@ -9733,13 +9745,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44978</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9766,7 +9778,7 @@
       <c r="I57" t="n">
         <v>0.3</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44978</v>
       </c>
       <c r="K57" t="n">
@@ -9779,13 +9791,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>45049</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9812,7 +9824,7 @@
       <c r="I58" t="n">
         <v>0.21</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>45049</v>
       </c>
       <c r="K58" t="n">
@@ -9825,13 +9837,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>45139</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9858,7 +9870,7 @@
       <c r="I59" t="n">
         <v>0.21</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>45139</v>
       </c>
       <c r="K59" t="n">
@@ -9871,13 +9883,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9904,7 +9916,7 @@
       <c r="I60" t="n">
         <v>0.46</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="K60" t="n">
@@ -9917,13 +9929,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45337</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -9950,7 +9962,7 @@
       <c r="I61" t="n">
         <v>0.66</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45337</v>
       </c>
       <c r="K61" t="n">
@@ -9963,13 +9975,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -9996,7 +10008,7 @@
       <c r="I62" t="n">
         <v>0.8300000000000001</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="K62" t="n">
@@ -10009,13 +10021,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45503</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10042,7 +10054,7 @@
       <c r="I63" t="n">
         <v>1.05</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45503</v>
       </c>
       <c r="K63" t="n">
@@ -10055,13 +10067,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45594</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10088,7 +10100,7 @@
       <c r="I64" t="n">
         <v>1.54</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45594</v>
       </c>
       <c r="K64" t="n">
@@ -10101,13 +10113,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45700</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10134,7 +10146,7 @@
       <c r="I65" t="n">
         <v>1.57</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45700</v>
       </c>
       <c r="K65" t="n">
@@ -10147,13 +10159,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45776</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10180,7 +10192,7 @@
       <c r="I66" t="n">
         <v>1.75</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45776</v>
       </c>
       <c r="K66" t="n">
@@ -10193,13 +10205,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45867</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10226,7 +10238,7 @@
       <c r="I67" t="n">
         <v>1.78</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45867</v>
       </c>
       <c r="K67" t="n">
@@ -10239,13 +10251,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45958</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10272,7 +10284,7 @@
       <c r="I68" t="n">
         <v>1.46</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45958</v>
       </c>
       <c r="K68" t="n">
@@ -10285,13 +10297,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>46065</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10318,7 +10330,7 @@
       <c r="I69" t="n">
         <v>1.39</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>46065</v>
       </c>
       <c r="K69" t="n">
@@ -10331,13 +10343,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>46141</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10364,7 +10376,7 @@
       <c r="I70" t="n">
         <v>2.01</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>46141</v>
       </c>
       <c r="K70" t="n">
@@ -10377,13 +10389,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46248</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10404,7 +10416,7 @@
       <c r="I71" t="n">
         <v>2.17</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46248</v>
       </c>
       <c r="K71" t="n">
@@ -10441,52 +10453,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40390</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40396</v>
       </c>
       <c r="C2" t="n">
@@ -10515,10 +10527,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40482</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40490</v>
       </c>
       <c r="C3" t="n">
@@ -10547,10 +10559,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40574</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40626</v>
       </c>
       <c r="C4" t="n">
@@ -10579,10 +10591,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40663</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40673</v>
       </c>
       <c r="C5" t="n">
@@ -10611,10 +10623,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40755</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40764</v>
       </c>
       <c r="C6" t="n">
@@ -10643,10 +10655,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40847</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40850</v>
       </c>
       <c r="C7" t="n">
@@ -10675,10 +10687,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40939</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40956</v>
       </c>
       <c r="C8" t="n">
@@ -10707,10 +10719,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>41121</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>41127</v>
       </c>
       <c r="C9" t="n">
@@ -10739,10 +10751,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>41213</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>41221</v>
       </c>
       <c r="C10" t="n">
@@ -10771,10 +10783,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>41305</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>41331</v>
       </c>
       <c r="C11" t="n">
@@ -10803,10 +10815,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>41394</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>41401</v>
       </c>
       <c r="C12" t="n">
@@ -10835,10 +10847,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41486</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41492</v>
       </c>
       <c r="C13" t="n">
@@ -10867,10 +10879,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41578</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41583</v>
       </c>
       <c r="C14" t="n">
@@ -10899,10 +10911,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41670</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41691</v>
       </c>
       <c r="C15" t="n">
@@ -10931,10 +10943,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41759</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41767</v>
       </c>
       <c r="C16" t="n">
@@ -10963,10 +10975,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41845</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41852</v>
       </c>
       <c r="C17" t="n">
@@ -10995,10 +11007,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41943</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41947</v>
       </c>
       <c r="C18" t="n">
@@ -11027,10 +11039,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>42035</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>42055</v>
       </c>
       <c r="C19" t="n">
@@ -11059,10 +11071,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>42125</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>42132</v>
       </c>
       <c r="C20" t="n">
@@ -11091,10 +11103,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>42213</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>42220</v>
       </c>
       <c r="C21" t="n">
@@ -11123,10 +11135,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>42300</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>42307</v>
       </c>
       <c r="C22" t="n">
@@ -11155,10 +11167,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>42400</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>42418</v>
       </c>
       <c r="C23" t="n">
@@ -11187,10 +11199,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42490</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42495</v>
       </c>
       <c r="C24" t="n">
@@ -11219,10 +11231,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42582</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42584</v>
       </c>
       <c r="C25" t="n">
@@ -11251,10 +11263,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42674</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42676</v>
       </c>
       <c r="C26" t="n">
@@ -11283,10 +11295,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42766</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42788</v>
       </c>
       <c r="C27" t="n">
@@ -11315,10 +11327,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42853</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42860</v>
       </c>
       <c r="C28" t="n">
@@ -11347,10 +11359,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42930</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42944</v>
       </c>
       <c r="C29" t="n">
@@ -11379,10 +11391,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>43039</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>43046</v>
       </c>
       <c r="C30" t="n">
@@ -11411,10 +11423,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>43131</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="C31" t="n">
@@ -11443,10 +11455,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>43217</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>43224</v>
       </c>
       <c r="C32" t="n">
@@ -11475,10 +11487,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>43308</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>43314</v>
       </c>
       <c r="C33" t="n">
@@ -11507,10 +11519,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>43398</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>43403</v>
       </c>
       <c r="C34" t="n">
@@ -11539,10 +11551,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43496</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43521</v>
       </c>
       <c r="C35" t="n">
@@ -11571,10 +11583,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43574</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="C36" t="n">
@@ -11603,10 +11615,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43665</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43678</v>
       </c>
       <c r="C37" t="n">
@@ -11635,10 +11647,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43759</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43768</v>
       </c>
       <c r="C38" t="n">
@@ -11667,10 +11679,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43861</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43875</v>
       </c>
       <c r="C39" t="n">
@@ -11699,10 +11711,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43952</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43958</v>
       </c>
       <c r="C40" t="n">
@@ -11731,10 +11743,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>44043</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>44049</v>
       </c>
       <c r="C41" t="n">
@@ -11763,10 +11775,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>44127</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>44133</v>
       </c>
       <c r="C42" t="n">
@@ -11795,10 +11807,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>44225</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>44237</v>
       </c>
       <c r="C43" t="n">
@@ -11827,10 +11839,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>44309</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>44315</v>
       </c>
       <c r="C44" t="n">
@@ -11859,10 +11871,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>44400</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>44407</v>
       </c>
       <c r="C45" t="n">
@@ -11891,10 +11903,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44498</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44505</v>
       </c>
       <c r="C46" t="n">
@@ -11923,10 +11935,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44596</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44608</v>
       </c>
       <c r="C47" t="n">
@@ -11955,10 +11967,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44680</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44691</v>
       </c>
       <c r="C48" t="n">
@@ -11987,10 +11999,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44778</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44782</v>
       </c>
       <c r="C49" t="n">
@@ -12019,10 +12031,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44865</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44873</v>
       </c>
       <c r="C50" t="n">
@@ -12051,10 +12063,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44973</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44978</v>
       </c>
       <c r="C51" t="n">
@@ -12083,10 +12095,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>45044</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>45049</v>
       </c>
       <c r="C52" t="n">
@@ -12115,10 +12127,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>45135</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>45139</v>
       </c>
       <c r="C53" t="n">
@@ -12147,10 +12159,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>45226</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="C54" t="n">
@@ -12179,10 +12191,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>45331</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>45337</v>
       </c>
       <c r="C55" t="n">
@@ -12211,10 +12223,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>45408</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="C56" t="n">
@@ -12243,10 +12255,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45499</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45503</v>
       </c>
       <c r="C57" t="n">
@@ -12275,10 +12287,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45590</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45594</v>
       </c>
       <c r="C58" t="n">
@@ -12307,10 +12319,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45695</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45700</v>
       </c>
       <c r="C59" t="n">
@@ -12339,10 +12351,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45772</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45776</v>
       </c>
       <c r="C60" t="n">
@@ -12371,10 +12383,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45863</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45867</v>
       </c>
       <c r="C61" t="n">
@@ -12403,10 +12415,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45954</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45958</v>
       </c>
       <c r="C62" t="n">
@@ -12435,10 +12447,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>46059</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>46065</v>
       </c>
       <c r="C63" t="n">
@@ -12467,10 +12479,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>46136</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>46141</v>
       </c>
       <c r="C64" t="n">
@@ -12517,12 +12529,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -12658,7 +12670,11 @@
           <t>Splits aplicados</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1985-09-04 1.5:1</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">

--- a/salidas/empresas/WELL.xlsx
+++ b/salidas/empresas/WELL.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>14.4244909286499</v>
+        <v>14.42450046539307</v>
       </c>
       <c r="C2" t="n">
         <v>37.18999862670898</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>14.13748359680176</v>
+        <v>14.13748073577881</v>
       </c>
       <c r="C3" t="n">
         <v>36.45000076293945</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>14.77745151519775</v>
+        <v>14.77744674682617</v>
       </c>
       <c r="C4" t="n">
         <v>38.09999847412109</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>13.74855518341064</v>
+        <v>13.74855613708496</v>
       </c>
       <c r="C5" t="n">
         <v>34.79999923706055</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>13.38903903961182</v>
+        <v>13.3890438079834</v>
       </c>
       <c r="C6" t="n">
         <v>33.88999938964844</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>13.80781745910645</v>
+        <v>13.80781555175781</v>
       </c>
       <c r="C7" t="n">
         <v>34.95000076293945</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>14.55055332183838</v>
+        <v>14.5505542755127</v>
       </c>
       <c r="C8" t="n">
         <v>36.18999862670898</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>16.05827522277832</v>
+        <v>16.05828285217285</v>
       </c>
       <c r="C9" t="n">
         <v>39.93999862670898</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>16.08642387390137</v>
+        <v>16.0864200592041</v>
       </c>
       <c r="C10" t="n">
         <v>40.0099983215332</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>16.85367393493652</v>
+        <v>16.85367965698242</v>
       </c>
       <c r="C11" t="n">
         <v>41.27999877929688</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>17.11905479431152</v>
+        <v>17.11905097961426</v>
       </c>
       <c r="C12" t="n">
         <v>41.93000030517578</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>17.71138191223145</v>
+        <v>17.71138000488281</v>
       </c>
       <c r="C13" t="n">
         <v>43.02000045776367</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>19.39656066894531</v>
+        <v>19.39656639099121</v>
       </c>
       <c r="C14" t="n">
         <v>46.81000137329102</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>18.56782150268555</v>
+        <v>18.56781959533691</v>
       </c>
       <c r="C15" t="n">
         <v>44.81000137329102</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>18.19075012207031</v>
+        <v>18.19074821472168</v>
       </c>
       <c r="C16" t="n">
         <v>43.90000152587891</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>18.74600219726562</v>
+        <v>18.74600410461426</v>
       </c>
       <c r="C17" t="n">
         <v>45.2400016784668</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>16.97439575195312</v>
+        <v>16.97440338134766</v>
       </c>
       <c r="C19" t="n">
         <v>40.36000061035156</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>15.43930721282959</v>
+        <v>15.43930339813232</v>
       </c>
       <c r="C20" t="n">
         <v>36.70999908447266</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>17.08816146850586</v>
+        <v>17.08816337585449</v>
       </c>
       <c r="C21" t="n">
         <v>39.90000152587891</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>19.25050735473633</v>
+        <v>19.2505054473877</v>
       </c>
       <c r="C23" t="n">
         <v>44.29000091552734</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>19.47651672363281</v>
+        <v>19.47652626037598</v>
       </c>
       <c r="C24" t="n">
         <v>44.81000137329102</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>19.42435646057129</v>
+        <v>19.42436599731445</v>
       </c>
       <c r="C25" t="n">
         <v>44.68999862670898</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>18.89234733581543</v>
+        <v>18.8923397064209</v>
       </c>
       <c r="C26" t="n">
         <v>42.81999969482422</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>18.15994834899902</v>
+        <v>18.15994644165039</v>
       </c>
       <c r="C27" t="n">
         <v>41.15999984741211</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>19.91152572631836</v>
+        <v>19.91152191162109</v>
       </c>
       <c r="C28" t="n">
         <v>45.13000106811523</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>21.67412185668945</v>
+        <v>21.67412376403809</v>
       </c>
       <c r="C29" t="n">
         <v>48.45000076293945</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>21.60701942443848</v>
+        <v>21.60702514648438</v>
       </c>
       <c r="C30" t="n">
         <v>48.29999923706055</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>19.90709114074707</v>
+        <v>19.90708923339844</v>
       </c>
       <c r="C31" t="n">
         <v>44.5</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>23.52693939208984</v>
+        <v>23.52693557739258</v>
       </c>
       <c r="C33" t="n">
         <v>51.86999893188477</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>20.18862724304199</v>
+        <v>20.18861770629883</v>
       </c>
       <c r="C35" t="n">
         <v>44.5099983215332</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>17.52893257141113</v>
+        <v>17.5289249420166</v>
       </c>
       <c r="C36" t="n">
         <v>38</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>19.46633720397949</v>
+        <v>19.46634101867676</v>
       </c>
       <c r="C37" t="n">
         <v>42.20000076293945</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>17.44129753112793</v>
+        <v>17.44128799438477</v>
       </c>
       <c r="C38" t="n">
         <v>37.81000137329102</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>14.46000385284424</v>
+        <v>14.46000194549561</v>
       </c>
       <c r="C39" t="n">
         <v>30.77000045776367</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>14.37542057037354</v>
+        <v>14.37541961669922</v>
       </c>
       <c r="C40" t="n">
         <v>30.59000015258789</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>16.01079750061035</v>
+        <v>16.01079940795898</v>
       </c>
       <c r="C41" t="n">
         <v>34.06999969482422</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>16.42239379882812</v>
+        <v>16.42239570617676</v>
       </c>
       <c r="C42" t="n">
         <v>34.25</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>19.20821189880371</v>
+        <v>19.20820808410645</v>
       </c>
       <c r="C44" t="n">
         <v>40.06000137329102</v>
@@ -1315,7 +1315,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>20.80127716064453</v>
+        <v>20.80127143859863</v>
       </c>
       <c r="C45" t="n">
         <v>42.70999908447266</v>
@@ -1334,7 +1334,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>20.27039909362793</v>
+        <v>20.27040672302246</v>
       </c>
       <c r="C46" t="n">
         <v>41.61999893188477</v>
@@ -1353,7 +1353,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>21.60975074768066</v>
+        <v>21.60974502563477</v>
       </c>
       <c r="C47" t="n">
         <v>44.36999893188477</v>
@@ -1372,7 +1372,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>22.04013824462891</v>
+        <v>22.04014778137207</v>
       </c>
       <c r="C48" t="n">
         <v>44.54999923706055</v>
@@ -1391,7 +1391,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>21.92636108398438</v>
+        <v>21.92634582519531</v>
       </c>
       <c r="C49" t="n">
         <v>44.31999969482422</v>
@@ -1429,7 +1429,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>21.29549217224121</v>
+        <v>21.29550170898438</v>
       </c>
       <c r="C51" t="n">
         <v>42.36000061035156</v>
@@ -1448,7 +1448,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>22.73831939697266</v>
+        <v>22.73832702636719</v>
       </c>
       <c r="C52" t="n">
         <v>45.22999954223633</v>
@@ -1467,7 +1467,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>22.58750534057617</v>
+        <v>22.58751106262207</v>
       </c>
       <c r="C53" t="n">
         <v>44.93000030517578</v>
@@ -1486,7 +1486,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>22.00115966796875</v>
+        <v>22.00115585327148</v>
       </c>
       <c r="C54" t="n">
         <v>43.08000183105469</v>
@@ -1505,7 +1505,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>21.51087760925293</v>
+        <v>21.51086616516113</v>
       </c>
       <c r="C55" t="n">
         <v>42.11999893188477</v>
@@ -1524,7 +1524,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>23.14002799987793</v>
+        <v>23.14001083374023</v>
       </c>
       <c r="C56" t="n">
         <v>45.31000137329102</v>
@@ -1543,7 +1543,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>23.81379890441895</v>
+        <v>23.81378173828125</v>
       </c>
       <c r="C57" t="n">
         <v>45.93000030517578</v>
@@ -1568,7 +1568,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>24.54485321044922</v>
+        <v>24.54485130310059</v>
       </c>
       <c r="C58" t="n">
         <v>47.34000015258789</v>
@@ -1593,7 +1593,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>26.49433517456055</v>
+        <v>26.49433708190918</v>
       </c>
       <c r="C59" t="n">
         <v>51.09999847412109</v>
@@ -1618,7 +1618,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>24.32845306396484</v>
+        <v>24.32846069335938</v>
       </c>
       <c r="C60" t="n">
         <v>46.27999877929688</v>
@@ -1643,7 +1643,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>25.04338645935059</v>
+        <v>25.04338073730469</v>
       </c>
       <c r="C61" t="n">
         <v>47.63999938964844</v>
@@ -1668,7 +1668,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>25.80035781860352</v>
+        <v>25.80035972595215</v>
       </c>
       <c r="C62" t="n">
         <v>49.08000183105469</v>
@@ -1693,7 +1693,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>27.84033393859863</v>
+        <v>27.84032440185547</v>
       </c>
       <c r="C63" t="n">
         <v>52.22000122070312</v>
@@ -1718,7 +1718,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>27.95761680603027</v>
+        <v>27.95761489868164</v>
       </c>
       <c r="C64" t="n">
         <v>52.43999862670898</v>
@@ -1747,7 +1747,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>28.66670227050781</v>
+        <v>28.66669464111328</v>
       </c>
       <c r="C65" t="n">
         <v>53.77000045776367</v>
@@ -1776,7 +1776,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>28.74825286865234</v>
+        <v>28.74824523925781</v>
       </c>
       <c r="C66" t="n">
         <v>53.18999862670898</v>
@@ -1834,7 +1834,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>28.52665138244629</v>
+        <v>28.52665328979492</v>
       </c>
       <c r="C68" t="n">
         <v>52.77999877929688</v>
@@ -1863,7 +1863,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>27.9657154083252</v>
+        <v>27.9657096862793</v>
       </c>
       <c r="C69" t="n">
         <v>50.95999908447266</v>
@@ -1892,7 +1892,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>25.68280410766602</v>
+        <v>25.68280982971191</v>
       </c>
       <c r="C70" t="n">
         <v>46.79999923706055</v>
@@ -1921,7 +1921,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>28.91510963439941</v>
+        <v>28.91510009765625</v>
       </c>
       <c r="C71" t="n">
         <v>52.68999862670898</v>
@@ -1950,7 +1950,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>27.90876197814941</v>
+        <v>27.90875816345215</v>
       </c>
       <c r="C72" t="n">
         <v>50.16999816894531</v>
@@ -1979,7 +1979,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>30.33415985107422</v>
+        <v>30.33415603637695</v>
       </c>
       <c r="C73" t="n">
         <v>54.52999877929688</v>
@@ -2008,7 +2008,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>31.82499694824219</v>
+        <v>31.82500076293945</v>
       </c>
       <c r="C74" t="n">
         <v>57.20999908447266</v>
@@ -2037,7 +2037,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>30.68080139160156</v>
+        <v>30.68079376220703</v>
       </c>
       <c r="C75" t="n">
         <v>54.43999862670898</v>
@@ -2066,7 +2066,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>30.97385597229004</v>
+        <v>30.97385025024414</v>
       </c>
       <c r="C76" t="n">
         <v>54.95999908447266</v>
@@ -2095,7 +2095,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>31.9544677734375</v>
+        <v>31.95447731018066</v>
       </c>
       <c r="C77" t="n">
         <v>56.70000076293945</v>
@@ -2124,7 +2124,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>31.67260932922363</v>
+        <v>31.67261695861816</v>
       </c>
       <c r="C78" t="n">
         <v>55.47000122070312</v>
@@ -2153,7 +2153,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>33.28850936889648</v>
+        <v>33.28850173950195</v>
       </c>
       <c r="C79" t="n">
         <v>58.29999923706055</v>
@@ -2182,7 +2182,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>35.5324821472168</v>
+        <v>35.53248596191406</v>
       </c>
       <c r="C80" t="n">
         <v>62.22999954223633</v>
@@ -2211,7 +2211,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>33.77027893066406</v>
+        <v>33.7702751159668</v>
       </c>
       <c r="C81" t="n">
         <v>58.43999862670898</v>
@@ -2240,7 +2240,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>33.36577606201172</v>
+        <v>33.36576843261719</v>
       </c>
       <c r="C82" t="n">
         <v>57.7400016784668</v>
@@ -2269,7 +2269,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>34.34236526489258</v>
+        <v>34.34236145019531</v>
       </c>
       <c r="C83" t="n">
         <v>59.43000030517578</v>
@@ -2298,7 +2298,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>34.45981979370117</v>
+        <v>34.45983123779297</v>
       </c>
       <c r="C84" t="n">
         <v>58.88999938964844</v>
@@ -2327,7 +2327,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>35.86420440673828</v>
+        <v>35.86421203613281</v>
       </c>
       <c r="C85" t="n">
         <v>61.29000091552734</v>
@@ -2356,7 +2356,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>36.77118682861328</v>
+        <v>36.77119445800781</v>
       </c>
       <c r="C86" t="n">
         <v>62.84000015258789</v>
@@ -2385,7 +2385,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>37.99441909790039</v>
+        <v>37.99443817138672</v>
       </c>
       <c r="C87" t="n">
         <v>64.13999938964844</v>
@@ -2414,7 +2414,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>40.22765350341797</v>
+        <v>40.22764587402344</v>
       </c>
       <c r="C88" t="n">
         <v>67.91000366210938</v>
@@ -2443,7 +2443,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>44.40977478027344</v>
+        <v>44.40976333618164</v>
       </c>
       <c r="C89" t="n">
         <v>74.97000122070312</v>
@@ -2472,7 +2472,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>40.7108039855957</v>
+        <v>40.71079635620117</v>
       </c>
       <c r="C90" t="n">
         <v>68.02999877929688</v>
@@ -2501,7 +2501,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>40.11238479614258</v>
+        <v>40.11238098144531</v>
       </c>
       <c r="C91" t="n">
         <v>67.02999877929688</v>
@@ -2559,7 +2559,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>37.21495819091797</v>
+        <v>37.2149543762207</v>
       </c>
       <c r="C93" t="n">
         <v>61.43999862670898</v>
@@ -2617,7 +2617,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>39.28044509887695</v>
+        <v>39.28043746948242</v>
       </c>
       <c r="C95" t="n">
         <v>64.84999847412109</v>
@@ -2646,7 +2646,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>34.32890319824219</v>
+        <v>34.32890701293945</v>
       </c>
       <c r="C96" t="n">
         <v>55.9900016784668</v>
@@ -2675,7 +2675,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>32.84512710571289</v>
+        <v>32.84512329101562</v>
       </c>
       <c r="C97" t="n">
         <v>53.56999969482422</v>
@@ -2704,7 +2704,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>35.51223373413086</v>
+        <v>35.51222610473633</v>
       </c>
       <c r="C98" t="n">
         <v>57.91999816894531</v>
@@ -2762,7 +2762,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>37.05998611450195</v>
+        <v>37.05999374389648</v>
       </c>
       <c r="C100" t="n">
         <v>59.59999847412109</v>
@@ -2791,7 +2791,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>39.2301139831543</v>
+        <v>39.23012161254883</v>
       </c>
       <c r="C101" t="n">
         <v>63.09000015258789</v>
@@ -2820,7 +2820,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>39.81460952758789</v>
+        <v>39.81462097167969</v>
       </c>
       <c r="C102" t="n">
         <v>63.22999954223633</v>
@@ -2878,7 +2878,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>40.06647491455078</v>
+        <v>40.06648635864258</v>
       </c>
       <c r="C104" t="n">
         <v>63.63000106811523</v>
@@ -2907,7 +2907,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>43.08811569213867</v>
+        <v>43.08811950683594</v>
       </c>
       <c r="C105" t="n">
         <v>67.58000183105469</v>
@@ -2936,7 +2936,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>39.76629257202148</v>
+        <v>39.76628112792969</v>
       </c>
       <c r="C106" t="n">
         <v>62.36999893188477</v>
@@ -2965,7 +2965,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>45.33880233764648</v>
+        <v>45.33880996704102</v>
       </c>
       <c r="C107" t="n">
         <v>71.11000061035156</v>
@@ -3023,7 +3023,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>48.78814697265625</v>
+        <v>48.78814315795898</v>
       </c>
       <c r="C109" t="n">
         <v>75.66999816894531</v>
@@ -3110,7 +3110,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>50.38698959350586</v>
+        <v>50.38701629638672</v>
       </c>
       <c r="C112" t="n">
         <v>77.36000061035156</v>
@@ -3197,7 +3197,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>43.24607849121094</v>
+        <v>43.24608612060547</v>
       </c>
       <c r="C115" t="n">
         <v>65.62999725341797</v>
@@ -3226,7 +3226,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>45.71051406860352</v>
+        <v>45.71051788330078</v>
       </c>
       <c r="C116" t="n">
         <v>69.37000274658203</v>
@@ -3255,7 +3255,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>42.25266265869141</v>
+        <v>42.25267028808594</v>
       </c>
       <c r="C117" t="n">
         <v>63.34999847412109</v>
@@ -3313,7 +3313,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>43.26646041870117</v>
+        <v>43.2664680480957</v>
       </c>
       <c r="C119" t="n">
         <v>64.87000274658203</v>
@@ -3371,7 +3371,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>45.95812606811523</v>
+        <v>45.9581413269043</v>
       </c>
       <c r="C121" t="n">
         <v>68.02999877929688</v>
@@ -3400,7 +3400,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>42.03314971923828</v>
+        <v>42.03315353393555</v>
       </c>
       <c r="C122" t="n">
         <v>62.22000122070312</v>
@@ -3458,7 +3458,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>47.48427200317383</v>
+        <v>47.48427581787109</v>
       </c>
       <c r="C124" t="n">
         <v>69.33999633789062</v>
@@ -3487,7 +3487,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>47.53907012939453</v>
+        <v>47.53905487060547</v>
       </c>
       <c r="C125" t="n">
         <v>69.41999816894531</v>
@@ -3516,7 +3516,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>47.74674224853516</v>
+        <v>47.74673843383789</v>
       </c>
       <c r="C126" t="n">
         <v>68.91000366210938</v>
@@ -3545,7 +3545,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>52.777099609375</v>
+        <v>52.77708435058594</v>
       </c>
       <c r="C127" t="n">
         <v>76.16999816894531</v>
@@ -3603,7 +3603,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>53.77407455444336</v>
+        <v>53.77406692504883</v>
       </c>
       <c r="C129" t="n">
         <v>76.75</v>
@@ -3632,7 +3632,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>52.38680648803711</v>
+        <v>52.38681793212891</v>
       </c>
       <c r="C130" t="n">
         <v>74.76999664306641</v>
@@ -3661,7 +3661,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>48.01481246948242</v>
+        <v>48.01482009887695</v>
       </c>
       <c r="C131" t="n">
         <v>68.52999877929688</v>
@@ -3719,7 +3719,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>47.51308441162109</v>
+        <v>47.51309204101562</v>
       </c>
       <c r="C133" t="n">
         <v>66.93000030517578</v>
@@ -3777,7 +3777,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>50.62614059448242</v>
+        <v>50.62613296508789</v>
       </c>
       <c r="C135" t="n">
         <v>70.37999725341797</v>
@@ -3806,7 +3806,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>50.94264602661133</v>
+        <v>50.94264221191406</v>
       </c>
       <c r="C136" t="n">
         <v>70.81999969482422</v>
@@ -3835,7 +3835,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>51.38862991333008</v>
+        <v>51.38862228393555</v>
       </c>
       <c r="C137" t="n">
         <v>71.44000244140625</v>
@@ -3864,7 +3864,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>52.83790969848633</v>
+        <v>52.8379020690918</v>
       </c>
       <c r="C138" t="n">
         <v>72.54000091552734</v>
@@ -3922,7 +3922,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>53.45703887939453</v>
+        <v>53.45702743530273</v>
       </c>
       <c r="C140" t="n">
         <v>73.38999938964844</v>
@@ -3951,7 +3951,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>53.9759635925293</v>
+        <v>53.97595596313477</v>
       </c>
       <c r="C141" t="n">
         <v>73.22000122070312</v>
@@ -3980,7 +3980,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>51.80867004394531</v>
+        <v>51.80866241455078</v>
       </c>
       <c r="C142" t="n">
         <v>70.27999877929688</v>
@@ -4009,7 +4009,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>49.36125183105469</v>
+        <v>49.36124801635742</v>
       </c>
       <c r="C143" t="n">
         <v>66.95999908447266</v>
@@ -4038,7 +4038,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>50.37287902832031</v>
+        <v>50.37289047241211</v>
       </c>
       <c r="C144" t="n">
         <v>67.45999908447266</v>
@@ -4096,7 +4096,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>44.78004455566406</v>
+        <v>44.78004837036133</v>
       </c>
       <c r="C146" t="n">
         <v>59.97000122070312</v>
@@ -4125,7 +4125,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>39.82667922973633</v>
+        <v>39.82667541503906</v>
       </c>
       <c r="C147" t="n">
         <v>52.5</v>
@@ -4154,7 +4154,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>41.29078674316406</v>
+        <v>41.29077911376953</v>
       </c>
       <c r="C148" t="n">
         <v>54.43000030517578</v>
@@ -4212,7 +4212,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>44.42138671875</v>
+        <v>44.42139434814453</v>
       </c>
       <c r="C150" t="n">
         <v>57.65000152587891</v>
@@ -4241,7 +4241,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>48.30489349365234</v>
+        <v>48.30488586425781</v>
       </c>
       <c r="C151" t="n">
         <v>62.68999862670898</v>
@@ -4270,7 +4270,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>48.23555374145508</v>
+        <v>48.23554611206055</v>
       </c>
       <c r="C152" t="n">
         <v>62.59999847412109</v>
@@ -4299,7 +4299,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>52.10724639892578</v>
+        <v>52.10726165771484</v>
       </c>
       <c r="C153" t="n">
         <v>66.70999908447266</v>
@@ -4328,7 +4328,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>50.24042129516602</v>
+        <v>50.24042510986328</v>
       </c>
       <c r="C154" t="n">
         <v>64.31999969482422</v>
@@ -4357,7 +4357,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>51.60734558105469</v>
+        <v>51.60736083984375</v>
       </c>
       <c r="C155" t="n">
         <v>66.06999969482422</v>
@@ -4386,7 +4386,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>57.21743774414062</v>
+        <v>57.21744155883789</v>
       </c>
       <c r="C156" t="n">
         <v>72.33000183105469</v>
@@ -4415,7 +4415,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>54.90754699707031</v>
+        <v>54.90752029418945</v>
       </c>
       <c r="C157" t="n">
         <v>69.41000366210938</v>
@@ -4444,7 +4444,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>61.29931640625</v>
+        <v>61.29933166503906</v>
       </c>
       <c r="C158" t="n">
         <v>77.48999786376953</v>
@@ -4473,7 +4473,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>59.46673202514648</v>
+        <v>59.46670532226562</v>
       </c>
       <c r="C159" t="n">
         <v>74.30999755859375</v>
@@ -4531,7 +4531,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>59.64276885986328</v>
+        <v>59.64277267456055</v>
       </c>
       <c r="C161" t="n">
         <v>74.52999877929688</v>
@@ -4560,7 +4560,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>65.73409271240234</v>
+        <v>65.73410797119141</v>
       </c>
       <c r="C162" t="n">
         <v>81.22000122070312</v>
@@ -4589,7 +4589,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>65.9849853515625</v>
+        <v>65.98500061035156</v>
       </c>
       <c r="C163" t="n">
         <v>81.52999877929688</v>
@@ -4647,7 +4647,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>73.20894622802734</v>
+        <v>73.20893859863281</v>
       </c>
       <c r="C165" t="n">
         <v>89.55999755859375</v>
@@ -4676,7 +4676,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>74.09995269775391</v>
+        <v>74.09993743896484</v>
       </c>
       <c r="C166" t="n">
         <v>90.65000152587891</v>
@@ -4705,7 +4705,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>74.13263702392578</v>
+        <v>74.13265228271484</v>
       </c>
       <c r="C167" t="n">
         <v>90.69000244140625</v>
@@ -4734,7 +4734,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>69.86128234863281</v>
+        <v>69.86128997802734</v>
       </c>
       <c r="C168" t="n">
         <v>84.56999969482422</v>
@@ -4763,7 +4763,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>67.55651092529297</v>
+        <v>67.55653381347656</v>
       </c>
       <c r="C169" t="n">
         <v>81.77999877929688</v>
@@ -4792,7 +4792,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>70.14215087890625</v>
+        <v>70.14215850830078</v>
       </c>
       <c r="C170" t="n">
         <v>84.91000366210938</v>
@@ -4850,7 +4850,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>38.19530868530273</v>
+        <v>38.1953125</v>
       </c>
       <c r="C172" t="n">
         <v>45.77999877929688</v>
@@ -4908,7 +4908,7 @@
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>42.91919326782227</v>
+        <v>42.91919708251953</v>
       </c>
       <c r="C174" t="n">
         <v>50.66999816894531</v>
@@ -4937,7 +4937,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>43.83399963378906</v>
+        <v>43.8339958190918</v>
       </c>
       <c r="C175" t="n">
         <v>51.75</v>
@@ -4966,7 +4966,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>45.36713027954102</v>
+        <v>45.36713409423828</v>
       </c>
       <c r="C176" t="n">
         <v>53.56000137329102</v>
@@ -4995,7 +4995,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>49.25077819824219</v>
+        <v>49.25077438354492</v>
       </c>
       <c r="C177" t="n">
         <v>57.52000045776367</v>
@@ -5024,7 +5024,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>47.17011642456055</v>
+        <v>47.17012023925781</v>
       </c>
       <c r="C178" t="n">
         <v>55.09000015258789</v>
@@ -5053,7 +5053,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>46.03989028930664</v>
+        <v>46.03987884521484</v>
       </c>
       <c r="C179" t="n">
         <v>53.77000045776367</v>
@@ -5111,7 +5111,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>55.94496154785156</v>
+        <v>55.94495010375977</v>
       </c>
       <c r="C181" t="n">
         <v>64.62000274658203</v>
@@ -5140,7 +5140,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>52.46462249755859</v>
+        <v>52.46462631225586</v>
       </c>
       <c r="C182" t="n">
         <v>60.59999847412109</v>
@@ -5169,7 +5169,7 @@
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>59.31538009643555</v>
+        <v>59.31539535522461</v>
       </c>
       <c r="C183" t="n">
         <v>67.90000152587891</v>
@@ -5198,7 +5198,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>62.57378768920898</v>
+        <v>62.57381057739258</v>
       </c>
       <c r="C184" t="n">
         <v>71.62999725341797</v>
@@ -5227,7 +5227,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>65.54393005371094</v>
+        <v>65.54393768310547</v>
       </c>
       <c r="C185" t="n">
         <v>75.02999877929688</v>
@@ -5256,7 +5256,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>65.85457611083984</v>
+        <v>65.85456848144531</v>
       </c>
       <c r="C186" t="n">
         <v>74.76999664306641</v>
@@ -5285,7 +5285,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>73.19134521484375</v>
+        <v>73.19132995605469</v>
       </c>
       <c r="C187" t="n">
         <v>83.09999847412109</v>
@@ -5314,7 +5314,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>76.50300598144531</v>
+        <v>76.50299072265625</v>
       </c>
       <c r="C188" t="n">
         <v>86.86000061035156</v>
@@ -5343,7 +5343,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>77.65010070800781</v>
+        <v>77.65009307861328</v>
       </c>
       <c r="C189" t="n">
         <v>87.52999877929688</v>
@@ -5401,7 +5401,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>71.32489776611328</v>
+        <v>71.32490539550781</v>
       </c>
       <c r="C191" t="n">
         <v>80.40000152587891</v>
@@ -5430,7 +5430,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>71.14018249511719</v>
+        <v>71.14017486572266</v>
       </c>
       <c r="C192" t="n">
         <v>79.62000274658203</v>
@@ -5459,7 +5459,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>76.63520050048828</v>
+        <v>76.63517761230469</v>
       </c>
       <c r="C193" t="n">
         <v>85.76999664306641</v>
@@ -5575,7 +5575,7 @@
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>81.72975921630859</v>
+        <v>81.72974395751953</v>
       </c>
       <c r="C197" t="n">
         <v>90.80999755859375</v>
@@ -5633,7 +5633,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>74.63235473632812</v>
+        <v>74.63236999511719</v>
       </c>
       <c r="C199" t="n">
         <v>82.34999847412109</v>
@@ -5662,7 +5662,7 @@
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>78.24843597412109</v>
+        <v>78.24842071533203</v>
       </c>
       <c r="C200" t="n">
         <v>86.33999633789062</v>
@@ -5691,7 +5691,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>70.00314331054688</v>
+        <v>70.00315093994141</v>
       </c>
       <c r="C201" t="n">
         <v>76.65000152587891</v>
@@ -5720,7 +5720,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>58.74237060546875</v>
+        <v>58.74236679077148</v>
       </c>
       <c r="C202" t="n">
         <v>64.31999969482422</v>
@@ -5749,7 +5749,7 @@
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>55.74679183959961</v>
+        <v>55.74679946899414</v>
       </c>
       <c r="C203" t="n">
         <v>61.04000091552734</v>
@@ -5778,7 +5778,7 @@
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>65.45594787597656</v>
+        <v>65.45595550537109</v>
       </c>
       <c r="C204" t="n">
         <v>71.02999877929688</v>
@@ -5807,7 +5807,7 @@
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>60.40599060058594</v>
+        <v>60.40598678588867</v>
       </c>
       <c r="C205" t="n">
         <v>65.55000305175781</v>
@@ -5836,7 +5836,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>69.15127563476562</v>
+        <v>69.15126800537109</v>
       </c>
       <c r="C206" t="n">
         <v>75.04000091552734</v>
@@ -5865,7 +5865,7 @@
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>68.86454772949219</v>
+        <v>68.86453247070312</v>
       </c>
       <c r="C207" t="n">
         <v>74.12000274658203</v>
@@ -5952,7 +5952,7 @@
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>69.85716247558594</v>
+        <v>69.85717010498047</v>
       </c>
       <c r="C210" t="n">
         <v>74.61000061035156</v>
@@ -5981,7 +5981,7 @@
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>75.73709869384766</v>
+        <v>75.73710632324219</v>
       </c>
       <c r="C211" t="n">
         <v>80.88999938964844</v>
@@ -6010,7 +6010,7 @@
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>76.91684722900391</v>
+        <v>76.91683959960938</v>
       </c>
       <c r="C212" t="n">
         <v>82.15000152587891</v>
@@ -6039,7 +6039,7 @@
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>78.16623687744141</v>
+        <v>78.16622924804688</v>
       </c>
       <c r="C213" t="n">
         <v>82.87999725341797</v>
@@ -6068,7 +6068,7 @@
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>77.26081848144531</v>
+        <v>77.26084136962891</v>
       </c>
       <c r="C214" t="n">
         <v>81.91999816894531</v>
@@ -6097,7 +6097,7 @@
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>78.85469818115234</v>
+        <v>78.85472106933594</v>
       </c>
       <c r="C215" t="n">
         <v>83.61000061035156</v>
@@ -6126,7 +6126,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>84.63291931152344</v>
+        <v>84.63291168212891</v>
       </c>
       <c r="C216" t="n">
         <v>89.09999847412109</v>
@@ -6155,7 +6155,7 @@
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>85.64926147460938</v>
+        <v>85.64926910400391</v>
       </c>
       <c r="C217" t="n">
         <v>90.16999816894531</v>
@@ -6184,7 +6184,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>82.17276763916016</v>
+        <v>82.17276000976562</v>
       </c>
       <c r="C218" t="n">
         <v>86.51000213623047</v>
@@ -6213,7 +6213,7 @@
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>88.10975646972656</v>
+        <v>88.10974884033203</v>
       </c>
       <c r="C219" t="n">
         <v>92.16000366210938</v>
@@ -6242,7 +6242,7 @@
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>89.33349609375</v>
+        <v>89.33351135253906</v>
       </c>
       <c r="C220" t="n">
         <v>93.44000244140625</v>
@@ -6271,7 +6271,7 @@
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>91.09263610839844</v>
+        <v>91.09264373779297</v>
       </c>
       <c r="C221" t="n">
         <v>95.27999877929688</v>
@@ -6300,7 +6300,7 @@
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>99.72740936279297</v>
+        <v>99.72740173339844</v>
       </c>
       <c r="C222" t="n">
         <v>103.6699981689453</v>
@@ -6329,7 +6329,7 @@
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>100.2853546142578</v>
+        <v>100.2853469848633</v>
       </c>
       <c r="C223" t="n">
         <v>104.25</v>
@@ -6387,7 +6387,7 @@
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>116.7568359375</v>
+        <v>116.7568283081055</v>
       </c>
       <c r="C225" t="n">
         <v>120.6800003051758</v>
@@ -6445,7 +6445,7 @@
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>130.4952392578125</v>
+        <v>130.4951934814453</v>
       </c>
       <c r="C227" t="n">
         <v>134.8800048828125</v>
@@ -6503,7 +6503,7 @@
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>122.536750793457</v>
+        <v>122.5367660522461</v>
       </c>
       <c r="C229" t="n">
         <v>126.0299987792969</v>
@@ -6561,7 +6561,7 @@
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>149.921875</v>
+        <v>149.9218902587891</v>
       </c>
       <c r="C231" t="n">
         <v>153.5099945068359</v>
@@ -6619,7 +6619,7 @@
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>149.0233917236328</v>
+        <v>149.0234069824219</v>
       </c>
       <c r="C233" t="n">
         <v>152.5899963378906</v>
@@ -6648,7 +6648,7 @@
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>151.3719940185547</v>
+        <v>151.3720092773438</v>
       </c>
       <c r="C234" t="n">
         <v>154.2799987792969</v>
@@ -6735,7 +6735,7 @@
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>165.8384552001953</v>
+        <v>165.8384704589844</v>
       </c>
       <c r="C237" t="n">
         <v>168.2799987792969</v>
